--- a/analysis/recap/sp-PRF.xlsx
+++ b/analysis/recap/sp-PRF.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,7 +476,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -486,7 +486,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -503,13 +503,13 @@
         <v>14298463</v>
       </c>
       <c r="H2" t="n">
-        <v>0.861271676300578</v>
+        <v>0.9079754601226994</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8764705882352941</v>
+        <v>0.8705882352941177</v>
       </c>
       <c r="J2" t="n">
-        <v>0.868804664723032</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="3">
@@ -520,7 +520,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -530,7 +530,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -547,13 +547,13 @@
         <v>30288239</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9096385542168675</v>
+        <v>0.8764705882352941</v>
       </c>
       <c r="I3" t="n">
-        <v>0.888235294117647</v>
+        <v>0.8764705882352941</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8988095238095238</v>
+        <v>0.8764705882352941</v>
       </c>
     </row>
     <row r="4">
@@ -564,7 +564,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -591,13 +591,13 @@
         <v>42511865</v>
       </c>
       <c r="H4" t="n">
-        <v>0.861271676300578</v>
+        <v>0.8588235294117647</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8764705882352941</v>
+        <v>0.8588235294117647</v>
       </c>
       <c r="J4" t="n">
-        <v>0.868804664723032</v>
+        <v>0.8588235294117647</v>
       </c>
     </row>
     <row r="5">
@@ -608,7 +608,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -635,13 +635,13 @@
         <v>50995999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9161676646706587</v>
+        <v>0.8614457831325302</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9</v>
+        <v>0.8411764705882353</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9080118694362018</v>
+        <v>0.8511904761904762</v>
       </c>
     </row>
     <row r="6">
@@ -652,7 +652,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -679,13 +679,13 @@
         <v>246773155</v>
       </c>
       <c r="H6" t="n">
-        <v>0.8855421686746988</v>
+        <v>0.861271676300578</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8647058823529412</v>
+        <v>0.8764705882352941</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8750000000000001</v>
+        <v>0.868804664723032</v>
       </c>
     </row>
     <row r="7">
@@ -696,7 +696,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -706,30 +706,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>14298463</v>
       </c>
       <c r="H7" t="n">
-        <v>0.861271676300578</v>
+        <v>0.9024390243902439</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8764705882352941</v>
+        <v>0.8705882352941177</v>
       </c>
       <c r="J7" t="n">
-        <v>0.868804664723032</v>
+        <v>0.8862275449101796</v>
       </c>
     </row>
     <row r="8">
@@ -740,7 +740,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -750,30 +750,30 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>30288239</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9096385542168675</v>
+        <v>0.8630952380952381</v>
       </c>
       <c r="I8" t="n">
-        <v>0.888235294117647</v>
+        <v>0.8529411764705882</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8988095238095238</v>
+        <v>0.8579881656804734</v>
       </c>
     </row>
     <row r="9">
@@ -784,7 +784,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -794,30 +794,30 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>42511865</v>
       </c>
       <c r="H9" t="n">
-        <v>0.861271676300578</v>
+        <v>0.8705882352941177</v>
       </c>
       <c r="I9" t="n">
-        <v>0.8764705882352941</v>
+        <v>0.8705882352941177</v>
       </c>
       <c r="J9" t="n">
-        <v>0.868804664723032</v>
+        <v>0.8705882352941176</v>
       </c>
     </row>
     <row r="10">
@@ -828,7 +828,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -838,30 +838,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>50995999</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9161676646706587</v>
+        <v>0.8869047619047619</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9</v>
+        <v>0.8764705882352941</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9080118694362018</v>
+        <v>0.8816568047337278</v>
       </c>
     </row>
     <row r="11">
@@ -872,7 +872,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -882,30 +882,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>246773155</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8855421686746988</v>
+        <v>0.8505747126436781</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8647058823529412</v>
+        <v>0.8705882352941177</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8750000000000001</v>
+        <v>0.8604651162790696</v>
       </c>
     </row>
     <row r="12">
@@ -916,7 +916,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -943,13 +943,13 @@
         <v>14298463</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8470588235294118</v>
+        <v>0.896969696969697</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8470588235294118</v>
+        <v>0.8705882352941177</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8470588235294118</v>
+        <v>0.8835820895522388</v>
       </c>
     </row>
     <row r="13">
@@ -960,7 +960,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -987,13 +987,13 @@
         <v>30288239</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9024390243902439</v>
+        <v>0.861271676300578</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8705882352941177</v>
+        <v>0.8764705882352941</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8862275449101796</v>
+        <v>0.868804664723032</v>
       </c>
     </row>
     <row r="14">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1031,13 +1031,13 @@
         <v>42511865</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8690476190476191</v>
+        <v>0.8662790697674418</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8588235294117647</v>
+        <v>0.8764705882352941</v>
       </c>
       <c r="J14" t="n">
-        <v>0.863905325443787</v>
+        <v>0.8713450292397661</v>
       </c>
     </row>
     <row r="15">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1075,13 +1075,13 @@
         <v>50995999</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8779069767441861</v>
+        <v>0.8848484848484849</v>
       </c>
       <c r="I15" t="n">
-        <v>0.888235294117647</v>
+        <v>0.8588235294117647</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8830409356725146</v>
+        <v>0.8716417910447761</v>
       </c>
     </row>
     <row r="16">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1119,13 +1119,13 @@
         <v>246773155</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8720930232558139</v>
+        <v>0.8862275449101796</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.8705882352941177</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8771929824561403</v>
+        <v>0.8783382789317508</v>
       </c>
     </row>
     <row r="17">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1156,20 +1156,20 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G17" t="n">
         <v>14298463</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8470588235294118</v>
+        <v>0.8647058823529412</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8470588235294118</v>
+        <v>0.8647058823529412</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8470588235294118</v>
+        <v>0.8647058823529412</v>
       </c>
     </row>
     <row r="18">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1200,20 +1200,20 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>30288239</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9024390243902439</v>
+        <v>0.861271676300578</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8705882352941177</v>
+        <v>0.8764705882352941</v>
       </c>
       <c r="J18" t="n">
-        <v>0.8862275449101796</v>
+        <v>0.868804664723032</v>
       </c>
     </row>
     <row r="19">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1244,20 +1244,20 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>42511865</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8690476190476191</v>
+        <v>0.8461538461538461</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8588235294117647</v>
+        <v>0.8411764705882353</v>
       </c>
       <c r="J19" t="n">
-        <v>0.863905325443787</v>
+        <v>0.8436578171091446</v>
       </c>
     </row>
     <row r="20">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1288,20 +1288,20 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G20" t="n">
         <v>50995999</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8779069767441861</v>
+        <v>0.875</v>
       </c>
       <c r="I20" t="n">
-        <v>0.888235294117647</v>
+        <v>0.8647058823529412</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8830409356725146</v>
+        <v>0.8698224852071006</v>
       </c>
     </row>
     <row r="21">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1332,20 +1332,20 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G21" t="n">
         <v>246773155</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8720930232558139</v>
+        <v>0.8757396449704142</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.8705882352941177</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8771929824561403</v>
+        <v>0.8731563421828908</v>
       </c>
     </row>
     <row r="22">
@@ -1356,7 +1356,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1380,16 +1380,16 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>30288239</v>
+        <v>14298463</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8793103448275862</v>
+        <v>0.8941176470588236</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8742857142857143</v>
+        <v>0.8685714285714285</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8767908309455588</v>
+        <v>0.8811594202898549</v>
       </c>
     </row>
     <row r="23">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1424,16 +1424,16 @@
         </is>
       </c>
       <c r="G23" t="n">
-        <v>42511865</v>
+        <v>30288239</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9080459770114943</v>
+        <v>0.8742857142857143</v>
       </c>
       <c r="I23" t="n">
-        <v>0.9028571428571428</v>
+        <v>0.8742857142857143</v>
       </c>
       <c r="J23" t="n">
-        <v>0.9054441260744985</v>
+        <v>0.8742857142857143</v>
       </c>
     </row>
     <row r="24">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1468,16 +1468,16 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>50995999</v>
+        <v>42511865</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9226190476190477</v>
+        <v>0.9156626506024096</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8857142857142857</v>
+        <v>0.8685714285714285</v>
       </c>
       <c r="J24" t="n">
-        <v>0.9037900874635569</v>
+        <v>0.8914956011730205</v>
       </c>
     </row>
     <row r="25">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1512,16 +1512,16 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>246773155</v>
+        <v>50995999</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8901734104046243</v>
+        <v>0.8850574712643678</v>
       </c>
       <c r="I25" t="n">
         <v>0.88</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8850574712643678</v>
+        <v>0.8825214899713467</v>
       </c>
     </row>
     <row r="26">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1552,20 +1552,20 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>14298463</v>
+        <v>246773155</v>
       </c>
       <c r="H26" t="n">
-        <v>0.8806818181818182</v>
+        <v>0.8959537572254336</v>
       </c>
       <c r="I26" t="n">
         <v>0.8857142857142857</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8831908831908831</v>
+        <v>0.8908045977011495</v>
       </c>
     </row>
     <row r="27">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1586,30 +1586,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>30288239</v>
+        <v>14298463</v>
       </c>
       <c r="H27" t="n">
-        <v>0.8793103448275862</v>
+        <v>0.888235294117647</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8742857142857143</v>
+        <v>0.8628571428571429</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8767908309455588</v>
+        <v>0.8753623188405797</v>
       </c>
     </row>
     <row r="28">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1630,30 +1630,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>42511865</v>
+        <v>30288239</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9080459770114943</v>
+        <v>0.893491124260355</v>
       </c>
       <c r="I28" t="n">
-        <v>0.9028571428571428</v>
+        <v>0.8628571428571429</v>
       </c>
       <c r="J28" t="n">
-        <v>0.9054441260744985</v>
+        <v>0.8779069767441861</v>
       </c>
     </row>
     <row r="29">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1674,30 +1674,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>50995999</v>
+        <v>42511865</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9226190476190477</v>
+        <v>0.893491124260355</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8857142857142857</v>
+        <v>0.8628571428571429</v>
       </c>
       <c r="J29" t="n">
-        <v>0.9037900874635569</v>
+        <v>0.8779069767441861</v>
       </c>
     </row>
     <row r="30">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1718,30 +1718,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>246773155</v>
+        <v>50995999</v>
       </c>
       <c r="H30" t="n">
-        <v>0.8901734104046243</v>
+        <v>0.9005847953216374</v>
       </c>
       <c r="I30" t="n">
         <v>0.88</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8850574712643678</v>
+        <v>0.8901734104046243</v>
       </c>
     </row>
     <row r="31">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1776,16 +1776,16 @@
         </is>
       </c>
       <c r="G31" t="n">
-        <v>14298463</v>
+        <v>246773155</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9226190476190477</v>
+        <v>0.9011627906976745</v>
       </c>
       <c r="I31" t="n">
         <v>0.8857142857142857</v>
       </c>
       <c r="J31" t="n">
-        <v>0.9037900874635569</v>
+        <v>0.8933717579250721</v>
       </c>
     </row>
     <row r="32">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1820,16 +1820,16 @@
         </is>
       </c>
       <c r="G32" t="n">
-        <v>30288239</v>
+        <v>14298463</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8895348837209303</v>
+        <v>0.8869047619047619</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8742857142857143</v>
+        <v>0.8514285714285714</v>
       </c>
       <c r="J32" t="n">
-        <v>0.8818443804034583</v>
+        <v>0.8688046647230321</v>
       </c>
     </row>
     <row r="33">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1864,16 +1864,16 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>42511865</v>
+        <v>30288239</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9107142857142857</v>
+        <v>0.9017341040462428</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8742857142857143</v>
+        <v>0.8914285714285715</v>
       </c>
       <c r="J33" t="n">
-        <v>0.8921282798833819</v>
+        <v>0.896551724137931</v>
       </c>
     </row>
     <row r="34">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="G34" t="n">
-        <v>50995999</v>
+        <v>42511865</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9226190476190477</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8857142857142857</v>
+        <v>0.8742857142857143</v>
       </c>
       <c r="J34" t="n">
-        <v>0.9037900874635569</v>
+        <v>0.8843930635838151</v>
       </c>
     </row>
     <row r="35">
@@ -1928,7 +1928,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1952,16 +1952,16 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>246773155</v>
+        <v>50995999</v>
       </c>
       <c r="H35" t="n">
-        <v>0.875</v>
+        <v>0.8895348837209303</v>
       </c>
       <c r="I35" t="n">
-        <v>0.88</v>
+        <v>0.8742857142857143</v>
       </c>
       <c r="J35" t="n">
-        <v>0.8774928774928775</v>
+        <v>0.8818443804034583</v>
       </c>
     </row>
     <row r="36">
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1987,25 +1987,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>14298463</v>
+        <v>246773155</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9226190476190477</v>
+        <v>0.8947368421052632</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8857142857142857</v>
+        <v>0.8742857142857143</v>
       </c>
       <c r="J36" t="n">
-        <v>0.9037900874635569</v>
+        <v>0.8843930635838151</v>
       </c>
     </row>
     <row r="37">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2036,20 +2036,20 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>30288239</v>
+        <v>14298463</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8895348837209303</v>
+        <v>0.8757396449704142</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8742857142857143</v>
+        <v>0.8457142857142858</v>
       </c>
       <c r="J37" t="n">
-        <v>0.8818443804034583</v>
+        <v>0.86046511627907</v>
       </c>
     </row>
     <row r="38">
@@ -2060,7 +2060,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2080,20 +2080,20 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>42511865</v>
+        <v>30288239</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9107142857142857</v>
+        <v>0.8742857142857143</v>
       </c>
       <c r="I38" t="n">
         <v>0.8742857142857143</v>
       </c>
       <c r="J38" t="n">
-        <v>0.8921282798833819</v>
+        <v>0.8742857142857143</v>
       </c>
     </row>
     <row r="39">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>t5-base</t>
+          <t>flan-t5-base</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2124,20 +2124,20 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>50995999</v>
+        <v>42511865</v>
       </c>
       <c r="H39" t="n">
-        <v>0.9226190476190477</v>
+        <v>0.8670520231213873</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8857142857142857</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="J39" t="n">
-        <v>0.9037900874635569</v>
+        <v>0.8620689655172413</v>
       </c>
     </row>
     <row r="40">
@@ -2148,40 +2148,1844 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
+          <t>flan-t5-base</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.9161676646706587</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.8742857142857143</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>flan-t5-base</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.8742857142857143</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.8742857142857143</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.8742857142857143</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>t5-base</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.8579545454545454</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.888235294117647</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.8728323699421965</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.8654970760233918</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.8705882352941177</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.8680351906158358</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.9415584415584416</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.8529411764705882</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.8950617283950618</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.893491124260355</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.888235294117647</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.8908554572271388</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.8959537572254336</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.9037900874635569</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.8563218390804598</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.8764705882352941</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.866279069767442</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.884393063583815</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.8921282798833819</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.8779069767441861</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.888235294117647</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.8830409356725146</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.901840490797546</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.8647058823529412</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.8828828828828829</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.8742857142857143</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.8869565217391304</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.8875739644970414</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.8849557522123893</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.9101796407185628</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.8941176470588236</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.9020771513353116</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.8855421686746988</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.8647058823529412</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.8750000000000001</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.8705882352941177</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.8705882352941177</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.8705882352941176</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.8596491228070176</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.8647058823529412</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.8621700879765396</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.8757396449704142</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.8705882352941177</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.8731563421828908</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.8941176470588236</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.8941176470588236</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.8941176470588236</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.8275862068965517</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.8470588235294118</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.8372093023255814</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>gen-scl-nat</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.8654970760233918</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.8705882352941177</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.8680351906158358</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
         <is>
           <t>paraphrase</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.8771929824561403</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.8670520231213873</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.9022988505747126</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.8971428571428571</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.8997134670487106</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.861271676300578</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.8514285714285714</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.8563218390804598</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.8901734104046243</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.8850574712643678</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
         <v>246773155</v>
       </c>
-      <c r="H40" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="I40" t="n">
+      <c r="H66" t="n">
+        <v>0.884393063583815</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.8742857142857143</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.8793103448275862</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.9011627906976745</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.8933717579250721</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.8850574712643678</v>
+      </c>
+      <c r="I68" t="n">
         <v>0.88</v>
       </c>
-      <c r="J40" t="n">
-        <v>0.8774928774928775</v>
+      <c r="J68" t="n">
+        <v>0.8825214899713467</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.8728323699421965</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.8628571428571429</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.8678160919540231</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.8914285714285715</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.8914285714285715</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.8914285714285715</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.8757062146892656</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.8806818181818181</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.893491124260355</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.8628571428571429</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.8779069767441861</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.9325153374233128</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.8685714285714285</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.8994082840236686</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.8941176470588236</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.8685714285714285</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.8811594202898549</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.9047619047619048</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.8685714285714285</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.8862973760932944</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>14298463</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.8959537572254336</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.8908045977011495</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>30288239</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.9161676646706587</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.8742857142857143</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.8947368421052632</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>42511865</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.9390243902439024</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.9085545722713865</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>50995999</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.8953488372093024</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.887608069164265</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>acos_drone_binary</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>t5-base</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>paraphrase</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>246773155</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.8895348837209303</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.8742857142857143</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.8818443804034583</v>
       </c>
     </row>
   </sheetData>

--- a/analysis/recap/sp-PRF.xlsx
+++ b/analysis/recap/sp-PRF.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:P81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,17 +454,47 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>precision</t>
+          <t>micro_precision</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>recall</t>
+          <t>micro_recall</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>f1</t>
+          <t>micro_f1</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>macro_precision</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>macro_recall</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>macro_f1</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>weighted_precision</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>weighted_recall</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>weighted_f1</t>
         </is>
       </c>
     </row>
@@ -503,13 +533,31 @@
         <v>14298463</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9079754601226994</v>
+        <v>0.9202453987730062</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8705882352941177</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.9009009009009008</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.9297520661157025</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.9110192837465564</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.9294117647058824</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.8952941176470588</v>
       </c>
     </row>
     <row r="3">
@@ -547,13 +595,31 @@
         <v>30288239</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8764705882352941</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8764705882352941</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8764705882352941</v>
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.90633608815427</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.9118457300275483</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.9008264462809917</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.8980392156862746</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.8807843137254902</v>
       </c>
     </row>
     <row r="4">
@@ -599,6 +665,24 @@
       <c r="J4" t="n">
         <v>0.8588235294117647</v>
       </c>
+      <c r="K4" t="n">
+        <v>0.8953168044077136</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.8966942148760332</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.8884297520661157</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.877450980392157</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.8588235294117647</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.8592156862745097</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -635,13 +719,31 @@
         <v>50995999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8614457831325302</v>
+        <v>0.8674698795180723</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8411764705882353</v>
+        <v>0.8470588235294118</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8511904761904762</v>
+        <v>0.8571428571428572</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.8980716253443527</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.8884297520661157</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.8859504132231404</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.877450980392157</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.8470588235294118</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.8519607843137254</v>
       </c>
     </row>
     <row r="6">
@@ -679,13 +781,31 @@
         <v>246773155</v>
       </c>
       <c r="H6" t="n">
-        <v>0.861271676300578</v>
+        <v>0.8728323699421965</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8764705882352941</v>
+        <v>0.888235294117647</v>
       </c>
       <c r="J6" t="n">
-        <v>0.868804664723032</v>
+        <v>0.8804664723032068</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.9049586776859506</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.9173553719008266</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.9016528925619836</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.8921568627450983</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.888235294117647</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.8792156862745096</v>
       </c>
     </row>
     <row r="7">
@@ -723,13 +843,31 @@
         <v>14298463</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9024390243902439</v>
+        <v>0.9085365853658537</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8705882352941177</v>
+        <v>0.8764705882352941</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8862275449101796</v>
+        <v>0.8922155688622755</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.9228650137741047</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.9049586776859504</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.9038567493112947</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.9225490196078432</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.8764705882352941</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.8870588235294117</v>
       </c>
     </row>
     <row r="8">
@@ -767,13 +905,31 @@
         <v>30288239</v>
       </c>
       <c r="H8" t="n">
-        <v>0.8630952380952381</v>
+        <v>0.8690476190476191</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8529411764705882</v>
+        <v>0.8588235294117647</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8579881656804734</v>
+        <v>0.863905325443787</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.8911845730027549</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.8939393939393941</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.8853994490358125</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.877450980392157</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.8588235294117647</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.8596078431372549</v>
       </c>
     </row>
     <row r="9">
@@ -819,6 +975,24 @@
       <c r="J9" t="n">
         <v>0.8705882352941176</v>
       </c>
+      <c r="K9" t="n">
+        <v>0.8925619834710745</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.8980716253443528</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.8870523415977961</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.8862745098039216</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.8705882352941177</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.869019607843137</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -863,6 +1037,24 @@
       <c r="J10" t="n">
         <v>0.8816568047337278</v>
       </c>
+      <c r="K10" t="n">
+        <v>0.9077134986225897</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.9049586776859505</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.8986225895316804</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.8990196078431373</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.8764705882352941</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.8788235294117646</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -899,13 +1091,31 @@
         <v>246773155</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8505747126436781</v>
+        <v>0.8563218390804598</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8705882352941177</v>
+        <v>0.8764705882352941</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8604651162790696</v>
+        <v>0.866279069767442</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.8980716253443528</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.915977961432507</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.8964187327823692</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.8784313725490198</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.8764705882352941</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.8658823529411762</v>
       </c>
     </row>
     <row r="12">
@@ -943,13 +1153,31 @@
         <v>14298463</v>
       </c>
       <c r="H12" t="n">
-        <v>0.896969696969697</v>
+        <v>0.9030303030303031</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8705882352941177</v>
+        <v>0.8764705882352941</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8835820895522388</v>
+        <v>0.8895522388059701</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.9256198347107438</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.9118457300275483</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.9107438016528926</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.9137254901960785</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.8764705882352941</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.8850980392156863</v>
       </c>
     </row>
     <row r="13">
@@ -987,13 +1215,31 @@
         <v>30288239</v>
       </c>
       <c r="H13" t="n">
-        <v>0.861271676300578</v>
+        <v>0.8728323699421965</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8764705882352941</v>
+        <v>0.888235294117647</v>
       </c>
       <c r="J13" t="n">
-        <v>0.868804664723032</v>
+        <v>0.8804664723032068</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.9063360881542701</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.9173553719008265</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.9035812672176309</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.8941176470588237</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.888235294117647</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.8819607843137254</v>
       </c>
     </row>
     <row r="14">
@@ -1031,13 +1277,31 @@
         <v>42511865</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8662790697674418</v>
+        <v>0.8779069767441861</v>
       </c>
       <c r="I14" t="n">
-        <v>0.8764705882352941</v>
+        <v>0.888235294117647</v>
       </c>
       <c r="J14" t="n">
-        <v>0.8713450292397661</v>
+        <v>0.8830409356725146</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.9118457300275483</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.9173553719008266</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.9074380165289256</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.8960784313725493</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.888235294117647</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.8835294117647058</v>
       </c>
     </row>
     <row r="15">
@@ -1075,13 +1339,31 @@
         <v>50995999</v>
       </c>
       <c r="H15" t="n">
-        <v>0.8848484848484849</v>
+        <v>0.8909090909090909</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8588235294117647</v>
+        <v>0.8647058823529412</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8716417910447761</v>
+        <v>0.8776119402985074</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.915977961432507</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.9035812672176309</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.8994490358126721</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.9068627450980393</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.8647058823529412</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.8719607843137254</v>
       </c>
     </row>
     <row r="16">
@@ -1119,13 +1401,31 @@
         <v>246773155</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8862275449101796</v>
+        <v>0.9041916167664671</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8705882352941177</v>
+        <v>0.888235294117647</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8783382789317508</v>
+        <v>0.8961424332344213</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.9242424242424243</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.915977961432507</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.9107438016528926</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.9186274509803922</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.888235294117647</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.892156862745098</v>
       </c>
     </row>
     <row r="17">
@@ -1163,13 +1463,31 @@
         <v>14298463</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8647058823529412</v>
+        <v>0.8764705882352941</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8647058823529412</v>
+        <v>0.8764705882352941</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8647058823529412</v>
+        <v>0.8764705882352941</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.9049586776859504</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.9104683195592287</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.897245179063361</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.8960784313725491</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.8764705882352941</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.8749019607843136</v>
       </c>
     </row>
     <row r="18">
@@ -1207,13 +1525,31 @@
         <v>30288239</v>
       </c>
       <c r="H18" t="n">
-        <v>0.861271676300578</v>
+        <v>0.8786127167630058</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8764705882352941</v>
+        <v>0.8941176470588236</v>
       </c>
       <c r="J18" t="n">
-        <v>0.868804664723032</v>
+        <v>0.8862973760932945</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.9090909090909092</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.9201101928374655</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.90633608815427</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.9000000000000001</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.8941176470588236</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.8878431372549018</v>
       </c>
     </row>
     <row r="19">
@@ -1251,13 +1587,31 @@
         <v>42511865</v>
       </c>
       <c r="H19" t="n">
-        <v>0.8461538461538461</v>
+        <v>0.8579881656804734</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8411764705882353</v>
+        <v>0.8529411764705882</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8436578171091446</v>
+        <v>0.8554572271386431</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.8774104683195594</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.8774104683195594</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.8707988980716252</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.8686274509803923</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.8529411764705882</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.8529411764705881</v>
       </c>
     </row>
     <row r="20">
@@ -1295,13 +1649,31 @@
         <v>50995999</v>
       </c>
       <c r="H20" t="n">
-        <v>0.875</v>
+        <v>0.8869047619047619</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8647058823529412</v>
+        <v>0.8764705882352941</v>
       </c>
       <c r="J20" t="n">
-        <v>0.8698224852071006</v>
+        <v>0.8816568047337278</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.9118457300275483</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.9090909090909092</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.9008264462809916</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.9039215686274511</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.8764705882352941</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.8788235294117646</v>
       </c>
     </row>
     <row r="21">
@@ -1339,13 +1711,31 @@
         <v>246773155</v>
       </c>
       <c r="H21" t="n">
-        <v>0.8757396449704142</v>
+        <v>0.8875739644970414</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8705882352941177</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="J21" t="n">
-        <v>0.8731563421828908</v>
+        <v>0.8849557522123893</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.9132231404958678</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.9132231404958677</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.9057851239669422</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.8970588235294119</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.8807843137254899</v>
       </c>
     </row>
     <row r="22">
@@ -1383,13 +1773,31 @@
         <v>14298463</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8941176470588236</v>
+        <v>0.9058823529411765</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8685714285714285</v>
+        <v>0.88</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8811594202898549</v>
+        <v>0.8927536231884058</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.9207988980716254</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.9048799685163323</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.9176190476190477</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.8857414965986392</v>
       </c>
     </row>
     <row r="23">
@@ -1427,13 +1835,31 @@
         <v>30288239</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8742857142857143</v>
+        <v>0.8857142857142857</v>
       </c>
       <c r="I23" t="n">
-        <v>0.8742857142857143</v>
+        <v>0.8857142857142857</v>
       </c>
       <c r="J23" t="n">
-        <v>0.8742857142857143</v>
+        <v>0.8857142857142857</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.9056473829201102</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.8977174340810707</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.9023809523809523</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.8836462585034013</v>
       </c>
     </row>
     <row r="24">
@@ -1471,13 +1897,31 @@
         <v>42511865</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9156626506024096</v>
+        <v>0.9216867469879518</v>
       </c>
       <c r="I24" t="n">
-        <v>0.8685714285714285</v>
+        <v>0.8742857142857143</v>
       </c>
       <c r="J24" t="n">
-        <v>0.8914956011730205</v>
+        <v>0.8973607038123167</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.9352617079889808</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.9118457300275483</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.9137741046831956</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.9304761904761906</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.8742857142857143</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.8889523809523807</v>
       </c>
     </row>
     <row r="25">
@@ -1515,13 +1959,31 @@
         <v>50995999</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8850574712643678</v>
+        <v>0.8908045977011494</v>
       </c>
       <c r="I25" t="n">
-        <v>0.88</v>
+        <v>0.8857142857142857</v>
       </c>
       <c r="J25" t="n">
-        <v>0.8825214899713467</v>
+        <v>0.8882521489971347</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.9152892561983471</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.9118457300275483</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.9054309327036602</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.9052380952380952</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.8863129251700679</v>
       </c>
     </row>
     <row r="26">
@@ -1567,6 +2029,24 @@
       <c r="J26" t="n">
         <v>0.8908045977011495</v>
       </c>
+      <c r="K26" t="n">
+        <v>0.915977961432507</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.9146005509641874</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.9057851239669423</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.9104761904761905</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.8866666666666666</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1603,13 +2083,31 @@
         <v>14298463</v>
       </c>
       <c r="H27" t="n">
-        <v>0.888235294117647</v>
+        <v>0.9</v>
       </c>
       <c r="I27" t="n">
-        <v>0.8628571428571429</v>
+        <v>0.8742857142857143</v>
       </c>
       <c r="J27" t="n">
-        <v>0.8753623188405797</v>
+        <v>0.8869565217391304</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.9125344352617081</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.9008264462809917</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.896615505706415</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.911904761904762</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.8742857142857143</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.8800272108843535</v>
       </c>
     </row>
     <row r="28">
@@ -1647,13 +2145,31 @@
         <v>30288239</v>
       </c>
       <c r="H28" t="n">
-        <v>0.893491124260355</v>
+        <v>0.8994082840236687</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8628571428571429</v>
+        <v>0.8685714285714285</v>
       </c>
       <c r="J28" t="n">
-        <v>0.8779069767441861</v>
+        <v>0.8837209302325582</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.9166666666666667</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.9035812672176308</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0.9001967729240458</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.911904761904762</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.8685714285714285</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.8769795918367345</v>
       </c>
     </row>
     <row r="29">
@@ -1691,13 +2207,31 @@
         <v>42511865</v>
       </c>
       <c r="H29" t="n">
-        <v>0.893491124260355</v>
+        <v>0.8994082840236687</v>
       </c>
       <c r="I29" t="n">
-        <v>0.8628571428571429</v>
+        <v>0.8685714285714285</v>
       </c>
       <c r="J29" t="n">
-        <v>0.8779069767441861</v>
+        <v>0.8837209302325582</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.9269972451790633</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.9035812672176309</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0.9055096418732782</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.9247619047619048</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.8685714285714285</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.883238095238095</v>
       </c>
     </row>
     <row r="30">
@@ -1735,13 +2269,31 @@
         <v>50995999</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9005847953216374</v>
+        <v>0.9064327485380117</v>
       </c>
       <c r="I30" t="n">
-        <v>0.88</v>
+        <v>0.8857142857142857</v>
       </c>
       <c r="J30" t="n">
-        <v>0.8901734104046243</v>
+        <v>0.8959537572254336</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.9290633608815427</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.9173553719008265</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0.9143250688705233</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.9233333333333333</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.8940952380952379</v>
       </c>
     </row>
     <row r="31">
@@ -1779,13 +2331,31 @@
         <v>246773155</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9011627906976745</v>
+        <v>0.9069767441860465</v>
       </c>
       <c r="I31" t="n">
-        <v>0.8857142857142857</v>
+        <v>0.8914285714285715</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8933717579250721</v>
+        <v>0.899135446685879</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.9228650137741047</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.9201101928374655</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0.9118457300275483</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.9190476190476191</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.8914285714285715</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.8935238095238094</v>
       </c>
     </row>
     <row r="32">
@@ -1823,13 +2393,31 @@
         <v>14298463</v>
       </c>
       <c r="H32" t="n">
-        <v>0.8869047619047619</v>
+        <v>0.8928571428571429</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8514285714285714</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="J32" t="n">
-        <v>0.8688046647230321</v>
+        <v>0.8746355685131195</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.9187327823691459</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.8994490358126721</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.8980716253443527</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.9095238095238095</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.8681904761904761</v>
       </c>
     </row>
     <row r="33">
@@ -1875,6 +2463,24 @@
       <c r="J33" t="n">
         <v>0.896551724137931</v>
       </c>
+      <c r="K33" t="n">
+        <v>0.9207988980716254</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.9187327823691461</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.9106650924832744</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.9176190476190477</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.8914285714285715</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.8939319727891156</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1911,13 +2517,31 @@
         <v>42511865</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.9005847953216374</v>
       </c>
       <c r="I34" t="n">
-        <v>0.8742857142857143</v>
+        <v>0.88</v>
       </c>
       <c r="J34" t="n">
-        <v>0.8843930635838151</v>
+        <v>0.8901734104046243</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.9207988980716254</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.9118457300275484</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.9076347894529713</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.9147619047619048</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.8866938775510205</v>
       </c>
     </row>
     <row r="35">
@@ -1955,13 +2579,31 @@
         <v>50995999</v>
       </c>
       <c r="H35" t="n">
-        <v>0.8895348837209303</v>
+        <v>0.8953488372093024</v>
       </c>
       <c r="I35" t="n">
-        <v>0.8742857142857143</v>
+        <v>0.88</v>
       </c>
       <c r="J35" t="n">
-        <v>0.8818443804034583</v>
+        <v>0.887608069164265</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.9209366391184574</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.9104683195592288</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.9073002754820938</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.9093333333333333</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.8840952380952382</v>
       </c>
     </row>
     <row r="36">
@@ -1999,13 +2641,31 @@
         <v>246773155</v>
       </c>
       <c r="H36" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.9005847953216374</v>
       </c>
       <c r="I36" t="n">
-        <v>0.8742857142857143</v>
+        <v>0.88</v>
       </c>
       <c r="J36" t="n">
-        <v>0.8843930635838151</v>
+        <v>0.8901734104046243</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.9207988980716254</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.9132231404958677</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.9062573789846519</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.9147619047619048</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.8838367346938775</v>
       </c>
     </row>
     <row r="37">
@@ -2043,13 +2703,31 @@
         <v>14298463</v>
       </c>
       <c r="H37" t="n">
-        <v>0.8757396449704142</v>
+        <v>0.8816568047337278</v>
       </c>
       <c r="I37" t="n">
-        <v>0.8457142857142858</v>
+        <v>0.8514285714285714</v>
       </c>
       <c r="J37" t="n">
-        <v>0.86046511627907</v>
+        <v>0.866279069767442</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.8966942148760332</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.8900826446280993</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.903809523809524</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.8514285714285714</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.8617142857142857</v>
       </c>
     </row>
     <row r="38">
@@ -2087,13 +2765,31 @@
         <v>30288239</v>
       </c>
       <c r="H38" t="n">
-        <v>0.8742857142857143</v>
+        <v>0.88</v>
       </c>
       <c r="I38" t="n">
-        <v>0.8742857142857143</v>
+        <v>0.88</v>
       </c>
       <c r="J38" t="n">
-        <v>0.8742857142857143</v>
+        <v>0.88</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.9084022038567493</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.9077134986225897</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.8990948445493901</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.9033333333333334</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.8813605442176869</v>
       </c>
     </row>
     <row r="39">
@@ -2131,13 +2827,31 @@
         <v>42511865</v>
       </c>
       <c r="H39" t="n">
-        <v>0.8670520231213873</v>
+        <v>0.8728323699421965</v>
       </c>
       <c r="I39" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8628571428571429</v>
       </c>
       <c r="J39" t="n">
-        <v>0.8620689655172413</v>
+        <v>0.8678160919540231</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.8960055096418733</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.8884297520661157</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.8822904368358915</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.8976190476190476</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.8628571428571429</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.868408163265306</v>
       </c>
     </row>
     <row r="40">
@@ -2183,6 +2897,24 @@
       <c r="J40" t="n">
         <v>0.8947368421052632</v>
       </c>
+      <c r="K40" t="n">
+        <v>0.9311294765840221</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.9104683195592286</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.91267217630854</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.921904761904762</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.8742857142857143</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.8866666666666666</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2219,13 +2951,31 @@
         <v>246773155</v>
       </c>
       <c r="H41" t="n">
-        <v>0.8742857142857143</v>
+        <v>0.8857142857142857</v>
       </c>
       <c r="I41" t="n">
-        <v>0.8742857142857143</v>
+        <v>0.8857142857142857</v>
       </c>
       <c r="J41" t="n">
-        <v>0.8742857142857143</v>
+        <v>0.8857142857142857</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.9111570247933884</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.9173553719008265</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.9007477371113736</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.9109523809523811</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.8828843537414965</v>
       </c>
     </row>
     <row r="42">
@@ -2263,13 +3013,31 @@
         <v>14298463</v>
       </c>
       <c r="H42" t="n">
-        <v>0.8579545454545454</v>
+        <v>0.875</v>
       </c>
       <c r="I42" t="n">
-        <v>0.888235294117647</v>
+        <v>0.9058823529411765</v>
       </c>
       <c r="J42" t="n">
-        <v>0.8728323699421965</v>
+        <v>0.8901734104046243</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.9132231404958681</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.9366391184573002</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.9137741046831955</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.9000000000000004</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.9058823529411765</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.8905882352941175</v>
       </c>
     </row>
     <row r="43">
@@ -2307,13 +3075,31 @@
         <v>30288239</v>
       </c>
       <c r="H43" t="n">
-        <v>0.8654970760233918</v>
+        <v>0.8830409356725146</v>
       </c>
       <c r="I43" t="n">
-        <v>0.8705882352941177</v>
+        <v>0.888235294117647</v>
       </c>
       <c r="J43" t="n">
-        <v>0.8680351906158358</v>
+        <v>0.8856304985337242</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.9104683195592287</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.9159779614325069</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.9060606060606063</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.888235294117647</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.8866666666666666</v>
       </c>
     </row>
     <row r="44">
@@ -2359,6 +3145,24 @@
       <c r="J44" t="n">
         <v>0.8950617283950618</v>
       </c>
+      <c r="K44" t="n">
+        <v>0.9517906336088154</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.9008264462809918</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.9179063360881542</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.9352941176470588</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.8529411764705882</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.8805882352941176</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2395,13 +3199,31 @@
         <v>50995999</v>
       </c>
       <c r="H45" t="n">
-        <v>0.893491124260355</v>
+        <v>0.9053254437869822</v>
       </c>
       <c r="I45" t="n">
-        <v>0.888235294117647</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
-        <v>0.8908554572271388</v>
+        <v>0.9026548672566372</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.9256198347107439</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.9297520661157026</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.9217630853994491</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.9098039215686275</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.8980392156862744</v>
       </c>
     </row>
     <row r="46">
@@ -2447,6 +3269,24 @@
       <c r="J46" t="n">
         <v>0.9037900874635569</v>
       </c>
+      <c r="K46" t="n">
+        <v>0.9201101928374656</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.9380165289256198</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.9201101928374656</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.915686274509804</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.9117647058823529</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.9043137254901962</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2483,13 +3323,31 @@
         <v>14298463</v>
       </c>
       <c r="H47" t="n">
-        <v>0.8563218390804598</v>
+        <v>0.8735632183908046</v>
       </c>
       <c r="I47" t="n">
-        <v>0.8764705882352941</v>
+        <v>0.8941176470588236</v>
       </c>
       <c r="J47" t="n">
-        <v>0.866279069767442</v>
+        <v>0.8837209302325582</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.9008264462809918</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.9146005509641872</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.8983471074380167</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.8970588235294119</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.8941176470588236</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.8854901960784314</v>
       </c>
     </row>
     <row r="48">
@@ -2527,13 +3385,31 @@
         <v>30288239</v>
       </c>
       <c r="H48" t="n">
-        <v>0.884393063583815</v>
+        <v>0.9017341040462428</v>
       </c>
       <c r="I48" t="n">
-        <v>0.9</v>
+        <v>0.9176470588235294</v>
       </c>
       <c r="J48" t="n">
-        <v>0.8921282798833819</v>
+        <v>0.9096209912536443</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.9228650137741047</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.931129476584022</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.9195592286501378</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0.9254901960784314</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.9176470588235294</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0.9137254901960783</v>
       </c>
     </row>
     <row r="49">
@@ -2571,13 +3447,31 @@
         <v>42511865</v>
       </c>
       <c r="H49" t="n">
-        <v>0.8779069767441861</v>
+        <v>0.8895348837209303</v>
       </c>
       <c r="I49" t="n">
-        <v>0.888235294117647</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
-        <v>0.8830409356725146</v>
+        <v>0.8947368421052631</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.9152892561983472</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.918732782369146</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.9109405745769383</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.9044117647058825</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.8947338935574227</v>
       </c>
     </row>
     <row r="50">
@@ -2615,13 +3509,31 @@
         <v>50995999</v>
       </c>
       <c r="H50" t="n">
-        <v>0.901840490797546</v>
+        <v>0.9079754601226994</v>
       </c>
       <c r="I50" t="n">
-        <v>0.8647058823529412</v>
+        <v>0.8705882352941177</v>
       </c>
       <c r="J50" t="n">
-        <v>0.8828828828828829</v>
+        <v>0.8888888888888888</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.9201101928374656</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.9035812672176311</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.9052341597796142</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.9068627450980393</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.8705882352941177</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.8801960784313725</v>
       </c>
     </row>
     <row r="51">
@@ -2667,6 +3579,24 @@
       <c r="J51" t="n">
         <v>0.8869565217391304</v>
       </c>
+      <c r="K51" t="n">
+        <v>0.9035812672176309</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.9214876033057852</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.9035812672176309</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.9039215686274511</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.8925490196078431</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2711,6 +3641,24 @@
       <c r="J52" t="n">
         <v>0.8823529411764706</v>
       </c>
+      <c r="K52" t="n">
+        <v>0.9118457300275484</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.9159779614325071</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.9060606060606061</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.8970588235294119</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.8803921568627449</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2747,13 +3695,31 @@
         <v>30288239</v>
       </c>
       <c r="H53" t="n">
-        <v>0.8875739644970414</v>
+        <v>0.8994082840236687</v>
       </c>
       <c r="I53" t="n">
-        <v>0.8823529411764706</v>
+        <v>0.8941176470588236</v>
       </c>
       <c r="J53" t="n">
-        <v>0.8849557522123893</v>
+        <v>0.8967551622418879</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.9242424242424244</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.9242424242424243</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.918181818181818</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.9039215686274512</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.8941176470588236</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0.8909803921568626</v>
       </c>
     </row>
     <row r="54">
@@ -2791,13 +3757,31 @@
         <v>42511865</v>
       </c>
       <c r="H54" t="n">
-        <v>0.9101796407185628</v>
+        <v>0.9161676646706587</v>
       </c>
       <c r="I54" t="n">
-        <v>0.8941176470588236</v>
+        <v>0.9</v>
       </c>
       <c r="J54" t="n">
-        <v>0.9020771513353116</v>
+        <v>0.9080118694362018</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.9393939393939396</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.931129476584022</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.9267217630853994</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.9284313725490199</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.9021568627450978</v>
       </c>
     </row>
     <row r="55">
@@ -2835,13 +3819,31 @@
         <v>50995999</v>
       </c>
       <c r="H55" t="n">
-        <v>0.8855421686746988</v>
+        <v>0.9036144578313253</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8647058823529412</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="J55" t="n">
-        <v>0.8750000000000001</v>
+        <v>0.8928571428571428</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.9366391184573002</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.9256198347107438</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.924793388429752</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.9107843137254903</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.888627450980392</v>
       </c>
     </row>
     <row r="56">
@@ -2879,13 +3881,31 @@
         <v>246773155</v>
       </c>
       <c r="H56" t="n">
-        <v>0.8705882352941177</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="I56" t="n">
-        <v>0.8705882352941177</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="J56" t="n">
-        <v>0.8705882352941176</v>
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.9118457300275484</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.9146005509641875</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.9063360881542701</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.8941176470588237</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0.8799999999999998</v>
       </c>
     </row>
     <row r="57">
@@ -2923,13 +3943,31 @@
         <v>14298463</v>
       </c>
       <c r="H57" t="n">
-        <v>0.8596491228070176</v>
+        <v>0.8713450292397661</v>
       </c>
       <c r="I57" t="n">
-        <v>0.8647058823529412</v>
+        <v>0.8764705882352941</v>
       </c>
       <c r="J57" t="n">
-        <v>0.8621700879765396</v>
+        <v>0.8739002932551321</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.8994490358126723</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.9035812672176309</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.8911845730027549</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0.8901960784313727</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.8764705882352941</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0.8713725490196078</v>
       </c>
     </row>
     <row r="58">
@@ -2967,13 +4005,31 @@
         <v>30288239</v>
       </c>
       <c r="H58" t="n">
-        <v>0.8757396449704142</v>
+        <v>0.8875739644970414</v>
       </c>
       <c r="I58" t="n">
-        <v>0.8705882352941177</v>
+        <v>0.8823529411764706</v>
       </c>
       <c r="J58" t="n">
-        <v>0.8731563421828908</v>
+        <v>0.8849557522123893</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.9077134986225898</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.9077134986225897</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.9016528925619833</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0.8921568627450983</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.8823529411764706</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0.8792156862745096</v>
       </c>
     </row>
     <row r="59">
@@ -3019,6 +4075,24 @@
       <c r="J59" t="n">
         <v>0.8941176470588236</v>
       </c>
+      <c r="K59" t="n">
+        <v>0.9201101928374658</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.9173553719008265</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.9115702479338843</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.9107843137254904</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.8941176470588236</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.8933333333333331</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3055,13 +4129,31 @@
         <v>50995999</v>
       </c>
       <c r="H60" t="n">
-        <v>0.8275862068965517</v>
+        <v>0.8505747126436781</v>
       </c>
       <c r="I60" t="n">
-        <v>0.8470588235294118</v>
+        <v>0.8705882352941177</v>
       </c>
       <c r="J60" t="n">
-        <v>0.8372093023255814</v>
+        <v>0.8604651162790696</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.8898071625344353</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.9077134986225895</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.8914600550964187</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.8647058823529413</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.8705882352941177</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.8599999999999998</v>
       </c>
     </row>
     <row r="61">
@@ -3099,13 +4191,31 @@
         <v>246773155</v>
       </c>
       <c r="H61" t="n">
-        <v>0.8654970760233918</v>
+        <v>0.8713450292397661</v>
       </c>
       <c r="I61" t="n">
-        <v>0.8705882352941177</v>
+        <v>0.8764705882352941</v>
       </c>
       <c r="J61" t="n">
-        <v>0.8680351906158358</v>
+        <v>0.8739002932551321</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.8966942148760332</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.9063360881542701</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.8931129476584023</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.8872549019607844</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.8764705882352941</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.8729411764705881</v>
       </c>
     </row>
     <row r="62">
@@ -3143,13 +4253,31 @@
         <v>14298463</v>
       </c>
       <c r="H62" t="n">
-        <v>0.8771929824561403</v>
+        <v>0.8830409356725146</v>
       </c>
       <c r="I62" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.8628571428571429</v>
       </c>
       <c r="J62" t="n">
-        <v>0.8670520231213873</v>
+        <v>0.8728323699421966</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.9077134986225897</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.9035812672176308</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.8950413223140496</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0.8923809523809525</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.8628571428571429</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.8645714285714284</v>
       </c>
     </row>
     <row r="63">
@@ -3195,6 +4323,24 @@
       <c r="J63" t="n">
         <v>0.8997134670487106</v>
       </c>
+      <c r="K63" t="n">
+        <v>0.9242424242424243</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.9256198347107439</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.9165289256198349</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0.9161904761904762</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.8971428571428571</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0.8975238095238095</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3239,6 +4385,24 @@
       <c r="J64" t="n">
         <v>0.8563218390804598</v>
       </c>
+      <c r="K64" t="n">
+        <v>0.8801652892561984</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.8829201101928376</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.8727272727272729</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0.8704761904761905</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.8514285714285714</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.8504761904761904</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3283,6 +4447,24 @@
       <c r="J65" t="n">
         <v>0.8850574712643678</v>
       </c>
+      <c r="K65" t="n">
+        <v>0.9056473829201102</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.90633608815427</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.89909484454939</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0.8957142857142857</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0.8802176870748298</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -3319,13 +4501,31 @@
         <v>246773155</v>
       </c>
       <c r="H66" t="n">
-        <v>0.884393063583815</v>
+        <v>0.8901734104046243</v>
       </c>
       <c r="I66" t="n">
-        <v>0.8742857142857143</v>
+        <v>0.88</v>
       </c>
       <c r="J66" t="n">
-        <v>0.8793103448275862</v>
+        <v>0.8850574712643678</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0.9056473829201103</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.9049586776859505</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.8979929161747345</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0.8957142857142857</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0.8798367346938774</v>
       </c>
     </row>
     <row r="67">
@@ -3363,13 +4563,31 @@
         <v>14298463</v>
       </c>
       <c r="H67" t="n">
-        <v>0.9011627906976745</v>
+        <v>0.9069767441860465</v>
       </c>
       <c r="I67" t="n">
-        <v>0.8857142857142857</v>
+        <v>0.8914285714285715</v>
       </c>
       <c r="J67" t="n">
-        <v>0.8933717579250721</v>
+        <v>0.899135446685879</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.9304407713498624</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.9228650137741048</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.9178276269185361</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0.9204761904761906</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.8914285714285715</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0.895455782312925</v>
       </c>
     </row>
     <row r="68">
@@ -3407,13 +4625,31 @@
         <v>30288239</v>
       </c>
       <c r="H68" t="n">
-        <v>0.8850574712643678</v>
+        <v>0.896551724137931</v>
       </c>
       <c r="I68" t="n">
-        <v>0.88</v>
+        <v>0.8914285714285715</v>
       </c>
       <c r="J68" t="n">
-        <v>0.8825214899713467</v>
+        <v>0.8939828080229227</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.9152892561983471</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.9132231404958678</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.9051554506099962</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0.9138095238095237</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.8914285714285715</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0.892408163265306</v>
       </c>
     </row>
     <row r="69">
@@ -3459,6 +4695,24 @@
       <c r="J69" t="n">
         <v>0.8857142857142857</v>
       </c>
+      <c r="K69" t="n">
+        <v>0.9015151515151516</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.9104683195592287</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.8982683982683983</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0.891904761904762</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0.8805986394557823</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3503,6 +4757,24 @@
       <c r="J70" t="n">
         <v>0.8678160919540231</v>
       </c>
+      <c r="K70" t="n">
+        <v>0.8946280991735537</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.8953168044077136</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.8880755608028337</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0.8785714285714286</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.8628571428571429</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0.8630748299319727</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3547,6 +4819,24 @@
       <c r="J71" t="n">
         <v>0.8914285714285715</v>
       </c>
+      <c r="K71" t="n">
+        <v>0.9125344352617081</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.9173553719008265</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.9070838252656436</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0.9014285714285715</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0.8914285714285715</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0.8882176870748297</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3583,13 +4873,31 @@
         <v>14298463</v>
       </c>
       <c r="H72" t="n">
-        <v>0.8757062146892656</v>
+        <v>0.8813559322033898</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8857142857142857</v>
+        <v>0.8914285714285715</v>
       </c>
       <c r="J72" t="n">
-        <v>0.8806818181818181</v>
+        <v>0.8863636363636365</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.9139118457300275</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.9228650137741047</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.9109405745769383</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0.8966666666666666</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.8914285714285715</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0.8863129251700681</v>
       </c>
     </row>
     <row r="73">
@@ -3627,13 +4935,31 @@
         <v>30288239</v>
       </c>
       <c r="H73" t="n">
-        <v>0.893491124260355</v>
+        <v>0.8994082840236687</v>
       </c>
       <c r="I73" t="n">
-        <v>0.8628571428571429</v>
+        <v>0.8685714285714285</v>
       </c>
       <c r="J73" t="n">
-        <v>0.8779069767441861</v>
+        <v>0.8837209302325582</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.918732782369146</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.9022038567493114</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.9005509641873278</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0.9114285714285715</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.8685714285714285</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0.8775238095238095</v>
       </c>
     </row>
     <row r="74">
@@ -3671,13 +4997,31 @@
         <v>42511865</v>
       </c>
       <c r="H74" t="n">
-        <v>0.9325153374233128</v>
+        <v>0.9386503067484663</v>
       </c>
       <c r="I74" t="n">
-        <v>0.8685714285714285</v>
+        <v>0.8742857142857143</v>
       </c>
       <c r="J74" t="n">
-        <v>0.8994082840236686</v>
+        <v>0.9053254437869822</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0.9517906336088154</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.9146005509641875</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.9245179063360882</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0.9428571428571428</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0.8742857142857143</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0.8958095238095237</v>
       </c>
     </row>
     <row r="75">
@@ -3723,6 +5067,24 @@
       <c r="J75" t="n">
         <v>0.8811594202898549</v>
       </c>
+      <c r="K75" t="n">
+        <v>0.9132231404958677</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.9035812672176308</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.8997245179063361</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0.9028571428571428</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.8685714285714285</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0.8748571428571428</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3759,13 +5121,31 @@
         <v>246773155</v>
       </c>
       <c r="H76" t="n">
-        <v>0.9047619047619048</v>
+        <v>0.9107142857142857</v>
       </c>
       <c r="I76" t="n">
-        <v>0.8685714285714285</v>
+        <v>0.8742857142857143</v>
       </c>
       <c r="J76" t="n">
-        <v>0.8862973760932944</v>
+        <v>0.8921282798833819</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.9256198347107438</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.9132231404958677</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.9104683195592287</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0.9142857142857143</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.8742857142857143</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0.8828571428571429</v>
       </c>
     </row>
     <row r="77">
@@ -3811,6 +5191,24 @@
       <c r="J77" t="n">
         <v>0.8908045977011495</v>
       </c>
+      <c r="K77" t="n">
+        <v>0.9207988980716254</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.9201101928374656</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.9134199134199136</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0.9042857142857142</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0.8870748299319728</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3847,13 +5245,31 @@
         <v>30288239</v>
       </c>
       <c r="H78" t="n">
-        <v>0.9161676646706587</v>
+        <v>0.9221556886227545</v>
       </c>
       <c r="I78" t="n">
-        <v>0.8742857142857143</v>
+        <v>0.88</v>
       </c>
       <c r="J78" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.9005847953216375</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.9338842975206612</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.9118457300275482</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.9140495867768595</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0.9257142857142857</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0.8921904761904762</v>
       </c>
     </row>
     <row r="79">
@@ -3891,13 +5307,31 @@
         <v>42511865</v>
       </c>
       <c r="H79" t="n">
-        <v>0.9390243902439024</v>
+        <v>0.9451219512195121</v>
       </c>
       <c r="I79" t="n">
-        <v>0.88</v>
+        <v>0.8857142857142857</v>
       </c>
       <c r="J79" t="n">
-        <v>0.9085545722713865</v>
+        <v>0.9144542772861357</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0.9545454545454546</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.9228650137741047</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.9316804407713498</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0.9457142857142857</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.8857142857142857</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0.9059047619047619</v>
       </c>
     </row>
     <row r="80">
@@ -3943,6 +5377,24 @@
       <c r="J80" t="n">
         <v>0.887608069164265</v>
       </c>
+      <c r="K80" t="n">
+        <v>0.9132231404958677</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.9090909090909091</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.9038567493112948</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0.9028571428571428</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0.8834285714285713</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3979,13 +5431,31 @@
         <v>246773155</v>
       </c>
       <c r="H81" t="n">
-        <v>0.8895348837209303</v>
+        <v>0.8953488372093024</v>
       </c>
       <c r="I81" t="n">
-        <v>0.8742857142857143</v>
+        <v>0.88</v>
       </c>
       <c r="J81" t="n">
-        <v>0.8818443804034583</v>
+        <v>0.887608069164265</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.9159779614325069</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.9159779614325069</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.9077134986225897</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0.9009523809523809</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0.8815238095238093</v>
       </c>
     </row>
   </sheetData>
